--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WS.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WS.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Ra463f5a08a6840b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rbf6fd3a352ba4f78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rda80e03ca2ff493b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R13a0f91336354d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rdf34adbe35d94103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rbba0feeae3d14388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R478b30779f0241fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rc0aae54bf654487b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Re3f9a05c5eba4b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rd9341b6c558144c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rb914a366cbc649ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R89d3246eb50e43f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R2bbef4d6585942ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R4adb49bd6caf44f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R1d3643307b5b48f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rff903c7fb94940b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R5d88cd651b4b4982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R353e0866139945bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rd7ed85980e714fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R6b566bd954b84458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R69880ff4c0b941c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R640cfb1683394270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd23863d208274070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R99efd4ecf33349c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rfdc3bd8e4d2245af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R361490a6cc9a492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rb14e3176c3f34e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rb73875f2513148d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Raca5a205a51e4fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R584c20f8f8424851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R5879baffd93349dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R03179b9b098640bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R2ad04c95edd94d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rfc3a2d8852964bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R3c4cc9eead624312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rd3d21f9f31154f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rc1daf4a7ab014d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R1698a826e93f47bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Ra538159311964601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R1793d4e21f204477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Ra7803e185fe24a32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R0871515e606e4bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R6ee40a6a53904158"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4133,6 +4134,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>高玄(コ・ヒョン)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・右道房</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
